--- a/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
+++ b/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pending" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>202609190200</t>
+          <t>202609190700</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -871,84 +871,78 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900012</t>
+          <t>HASLS22260802581</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>202609150600</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>THSRP</t>
-        </is>
-      </c>
+          <t>202609210600</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS (THAILAND) CO., LTD.</t>
+          <t>INDIGO LINE CO., LTD.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>THAI FOODS INTERNATIONAL CO.,LTD.</t>
+          <t>CHANG YI TRADING CO.,L TD</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>YEAST EXTRACT</t>
+          <t xml:space="preserve">FOODSTUFFS </t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REUQEST CONTIANER GOOD CONDITION FOR FOODSTUFF</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-10 (PAPERLESS CODE : 2829)
-CLS TIME @SRP : 10/09/2026 @23.59 
-</t>
+          <t xml:space="preserve">Pickup : 2026-09-11, Return : 2026-09-12 (1ST 14/09 RETURN W/O RENT) </t>
         </is>
       </c>
       <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="R4" s="4" t="n">
         <v>0</v>
@@ -1018,12 +1012,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900147</t>
+          <t>HASLS22260802598</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1033,53 +1027,54 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>202609171100</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPIYM</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>PRO 3 BUILD INTERNATIONAL CO., LTD.</t>
+          <t>SCGJWD LOGISTICS PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>ASK ME CO.,LTD</t>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOYS </t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>RESIN-PALLET,NO RED WALL CONTAINER,CLEAN CONTAINER NO OIL STAINS , NO RUSTY ,NO CUT OR HOLE</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-03, Return : 2026-09-04  (1ST RTN DD: 09/09/26 WO/RENT)</t>
+          <t>CY-RTN 11-14/09/26 (  INV  3031061262 )
+*PLS CHECK OPEN GATE BEFORE RETURN CTNR*</t>
         </is>
       </c>
       <c r="O5" s="4" t="n">
@@ -1089,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R5" s="4" t="n">
         <v>0</v>
@@ -1159,12 +1154,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900236</t>
+          <t>HASLS22260900183</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1174,58 +1169,62 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
+          <t>202609251600</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>THLKR</t>
+        </is>
+      </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPMIZ</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x30 </t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CARGO CARE LOGISTICS CO., LTD.</t>
+          <t>THAI KAWANISHI LIMITED</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>RIVER KWAI INTERNATIONAL FOOD INDUSTRY CO., LTD.</t>
+          <t>THAI QUALITY STARCH CO.,LTD.</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>SWEET CORN</t>
+          <t>NATIVE TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Good and Clean Container (Food Grade)
-(No leaks, no odors, and no oil stains.)</t>
+          <t>REQUEST FOOD GRADE / SMOOTH FLOOR / N O SMELL / UNDER DECK</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-02, Return : 2026-09-15</t>
+          <t>Pickup : 2026-09-12 = 6X20'GP, Pickup : 2026-09-14 = 24X20'GP  
+Return : 2026-09-15 // PAPERLESS: 2829 // CLS DATE@ LKB DD.22/09/26 @23.59 (1ST RETURN 17/09/26)</t>
         </is>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
@@ -1252,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y6" s="4" t="n">
         <v>0</v>
@@ -1316,7 +1315,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>202609230130</t>
+          <t>202609261500</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -1457,7 +1456,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>202610120700</t>
+          <t>202610130130</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -1581,108 +1580,391 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900591</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>SWAL</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>202610191500</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x25 </t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>DP WORLD LOGISTICS SOLUTIONS (THAILAND) COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>DP WORLD LOGISTICS SOLUTIONS (THAILAND) COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>SOYBEAN OIL</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>**DO NOT RELEASE CNTR WAIT APPROVE** *FLEXIBAG* SERVEY 2026-10-12</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>**DO NOT RELEASE CNTR WAIT APPROVE** *FLEXIBAG*
+SERVEY 2026-10-12 , Pickup : 2026-09-14, Return : 2026-09-15</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4">
+        <f>SUM(O9:W9)-X9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="4">
+        <f>MAX(0,O9-MAX(0,X9))</f>
+        <v/>
+      </c>
+      <c r="AB9" s="4">
+        <f>MAX(0,P9-MAX(0,X9-SUM(O9:O9)))</f>
+        <v/>
+      </c>
+      <c r="AC9" s="4">
+        <f>MAX(0,Q9-MAX(0,X9-SUM(O9:P9)))</f>
+        <v/>
+      </c>
+      <c r="AD9" s="4">
+        <f>MAX(0,R9-MAX(0,X9-SUM(O9:Q9)))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="4">
+        <f>MAX(0,S9-MAX(0,X9-SUM(O9:R9)))</f>
+        <v/>
+      </c>
+      <c r="AF9" s="4">
+        <f>MAX(0,T9-MAX(0,X9-SUM(O9:S9)))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="4">
+        <f>MAX(0,U9-MAX(0,X9-SUM(O9:T9)))</f>
+        <v/>
+      </c>
+      <c r="AH9" s="4">
+        <f>MAX(0,V9-MAX(0,X9-SUM(O9:U9)))</f>
+        <v/>
+      </c>
+      <c r="AI9" s="4">
+        <f>MAX(0,W9-MAX(0,X9-SUM(O9:V9)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260900638</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>202610011030</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>JPNAO</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx4 </t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>CLEARFREIGHT (THAILAND) COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>NIPPAN INTERCROP CO., LTD.</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>CORN COB MEAL</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-11, Return : 2026-09-12</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="4">
+        <f>SUM(O10:W10)-X10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="4">
+        <f>MAX(0,O10-MAX(0,X10))</f>
+        <v/>
+      </c>
+      <c r="AB10" s="4">
+        <f>MAX(0,P10-MAX(0,X10-SUM(O10:O10)))</f>
+        <v/>
+      </c>
+      <c r="AC10" s="4">
+        <f>MAX(0,Q10-MAX(0,X10-SUM(O10:P10)))</f>
+        <v/>
+      </c>
+      <c r="AD10" s="4">
+        <f>MAX(0,R10-MAX(0,X10-SUM(O10:Q10)))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="4">
+        <f>MAX(0,S10-MAX(0,X10-SUM(O10:R10)))</f>
+        <v/>
+      </c>
+      <c r="AF10" s="4">
+        <f>MAX(0,T10-MAX(0,X10-SUM(O10:S10)))</f>
+        <v/>
+      </c>
+      <c r="AG10" s="4">
+        <f>MAX(0,U10-MAX(0,X10-SUM(O10:T10)))</f>
+        <v/>
+      </c>
+      <c r="AH10" s="4">
+        <f>MAX(0,V10-MAX(0,X10-SUM(O10:U10)))</f>
+        <v/>
+      </c>
+      <c r="AI10" s="4">
+        <f>MAX(0,W10-MAX(0,X10-SUM(O10:V10)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5">
-        <f>SUM(O3:O8)</f>
-        <v/>
-      </c>
-      <c r="P9" s="5">
-        <f>SUM(P3:P8)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="5">
-        <f>SUM(Q3:Q8)</f>
-        <v/>
-      </c>
-      <c r="R9" s="5">
-        <f>SUM(R3:R8)</f>
-        <v/>
-      </c>
-      <c r="S9" s="5">
-        <f>SUM(S3:S8)</f>
-        <v/>
-      </c>
-      <c r="T9" s="5">
-        <f>SUM(T3:T8)</f>
-        <v/>
-      </c>
-      <c r="U9" s="5">
-        <f>SUM(U3:U8)</f>
-        <v/>
-      </c>
-      <c r="V9" s="5">
-        <f>SUM(V3:V8)</f>
-        <v/>
-      </c>
-      <c r="W9" s="5">
-        <f>SUM(W3:W8)</f>
-        <v/>
-      </c>
-      <c r="X9" s="5">
-        <f>SUM(X3:X8)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="5" t="n"/>
-      <c r="Z9" s="5">
-        <f>SUM(Z3:Z8)</f>
-        <v/>
-      </c>
-      <c r="AA9" s="5">
-        <f>SUM(AA3:AA8)</f>
-        <v/>
-      </c>
-      <c r="AB9" s="5">
-        <f>SUM(AB3:AB8)</f>
-        <v/>
-      </c>
-      <c r="AC9" s="5">
-        <f>SUM(AC3:AC8)</f>
-        <v/>
-      </c>
-      <c r="AD9" s="5">
-        <f>SUM(AD3:AD8)</f>
-        <v/>
-      </c>
-      <c r="AE9" s="5">
-        <f>SUM(AE3:AE8)</f>
-        <v/>
-      </c>
-      <c r="AF9" s="5">
-        <f>SUM(AF3:AF8)</f>
-        <v/>
-      </c>
-      <c r="AG9" s="5">
-        <f>SUM(AG3:AG8)</f>
-        <v/>
-      </c>
-      <c r="AH9" s="5">
-        <f>SUM(AH3:AH8)</f>
-        <v/>
-      </c>
-      <c r="AI9" s="5">
-        <f>SUM(AI3:AI8)</f>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5">
+        <f>SUM(O3:O10)</f>
+        <v/>
+      </c>
+      <c r="P11" s="5">
+        <f>SUM(P3:P10)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="5">
+        <f>SUM(Q3:Q10)</f>
+        <v/>
+      </c>
+      <c r="R11" s="5">
+        <f>SUM(R3:R10)</f>
+        <v/>
+      </c>
+      <c r="S11" s="5">
+        <f>SUM(S3:S10)</f>
+        <v/>
+      </c>
+      <c r="T11" s="5">
+        <f>SUM(T3:T10)</f>
+        <v/>
+      </c>
+      <c r="U11" s="5">
+        <f>SUM(U3:U10)</f>
+        <v/>
+      </c>
+      <c r="V11" s="5">
+        <f>SUM(V3:V10)</f>
+        <v/>
+      </c>
+      <c r="W11" s="5">
+        <f>SUM(W3:W10)</f>
+        <v/>
+      </c>
+      <c r="X11" s="5">
+        <f>SUM(X3:X10)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="5" t="n"/>
+      <c r="Z11" s="5">
+        <f>SUM(Z3:Z10)</f>
+        <v/>
+      </c>
+      <c r="AA11" s="5">
+        <f>SUM(AA3:AA10)</f>
+        <v/>
+      </c>
+      <c r="AB11" s="5">
+        <f>SUM(AB3:AB10)</f>
+        <v/>
+      </c>
+      <c r="AC11" s="5">
+        <f>SUM(AC3:AC10)</f>
+        <v/>
+      </c>
+      <c r="AD11" s="5">
+        <f>SUM(AD3:AD10)</f>
+        <v/>
+      </c>
+      <c r="AE11" s="5">
+        <f>SUM(AE3:AE10)</f>
+        <v/>
+      </c>
+      <c r="AF11" s="5">
+        <f>SUM(AF3:AF10)</f>
+        <v/>
+      </c>
+      <c r="AG11" s="5">
+        <f>SUM(AG3:AG10)</f>
+        <v/>
+      </c>
+      <c r="AH11" s="5">
+        <f>SUM(AH3:AH10)</f>
+        <v/>
+      </c>
+      <c r="AI11" s="5">
+        <f>SUM(AI3:AI10)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AI8"/>
+  <autoFilter ref="A2:AI10"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AI1"/>
   </mergeCells>

--- a/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
+++ b/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
@@ -725,25 +725,25 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801418</t>
+          <t>HASLS22260801854</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n"/>
+          <t>202609230900</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -751,42 +751,42 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x10 </t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>YEARRAKARN CO., LTD.</t>
+          <t>SCG INTERNATIONAL CORPORATION CO., LTD.</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NON-DAIRY CERAMER </t>
+          <t>WHITE CLINKER</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>Request: Food Grade Container Only</t>
+          <t>Container clean, No Oil, No Rust and Loading by Forklift</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P3" s="4" t="n">
         <v>0</v>
@@ -856,25 +856,25 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801963</t>
+          <t>HASLS22260802152</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>202609221600</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n"/>
+          <t>202609211200</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -887,31 +887,31 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x10 </t>
+          <t xml:space="preserve">20'x8 </t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>SCG INTERNATIONAL CORPORATION CO., LTD.</t>
+          <t>M.S.K. FERTILIZER CO.,LTD</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>WHITE CLINKER</t>
+          <t>FERTILIZER NON DG</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Container clean, No Oil, No Rust and Loading by Forklift</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M4" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>0</v>
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0</v>
@@ -987,68 +987,72 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802334</t>
+          <t>HASLS22260802514</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>202609211000</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
+          <t>202609270600</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>THSRP</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x6 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>SUKASAEM WATTANA CO.,LTD.</t>
+          <t>TOYOX ASIA (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>TILE ADHESIVE AND TILE GROUT</t>
+          <t>TOYOX PRESSURE HOSES</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>RQS CLEAN &amp; GOOD CONTAINER CONDITION.</t>
+          <t>REQ. GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M5" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="4" t="n">
         <v>0</v>
@@ -1118,37 +1122,33 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802514</t>
+          <t>HASLS22260802581</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>202609271400</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>THSRP</t>
-        </is>
-      </c>
+          <t>202609222100</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1158,22 +1158,22 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>TOYOX ASIA (THAILAND) CO., LTD.</t>
+          <t>CHANG YI TRADING CO.,L TD</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>TOYOX PRESSURE HOSES</t>
+          <t xml:space="preserve">FOODSTUFFS </t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>REQ. GOOD AND CLEAN CONTAINER</t>
+          <t>REUQEST CONTIANER GOOD CONDITION FOR FOODSTUFF</t>
         </is>
       </c>
       <c r="M6" s="4" t="n">
@@ -1253,25 +1253,25 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802526</t>
+          <t>HASLS22260802630</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>202609211000</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n"/>
+          <t>202609241200</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1289,22 +1289,22 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>NUMWATTANA PACK &amp; PRINT CO., LTD.</t>
+          <t>FOMOTHAI CORPORATION CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>STEEL PLATE</t>
+          <t xml:space="preserve">AZOXYSTROBIN 25% W/V (23% W/W) SC </t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Request Good and No Leakage Container / UPGRADE CNTR 30 TONS</t>
+          <t>**APPROVAL BY MR.JEONG-YOUNG UM DD.03/09/2026** (DG UN NO : 3082 / CLASS 9)</t>
         </is>
       </c>
       <c r="M7" s="4" t="n">
@@ -1384,25 +1384,25 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802581</t>
+          <t>HASLS22260900108</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n"/>
+          <t>202609241200</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1420,22 +1420,22 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>CHANG YI TRADING CO.,L TD</t>
+          <t>YEARRAKARN CO., LTD.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOODSTUFFS </t>
+          <t>NON-DAIRY CERAMER</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>REUQEST CONTIANER GOOD CONDITION FOR FOODSTUFF</t>
+          <t>FOOD GRADE CONTAINER</t>
         </is>
       </c>
       <c r="M8" s="4" t="n">
@@ -1515,68 +1515,69 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802598</t>
+          <t>HASLS22260900236</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>202609220200</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n"/>
+          <t>202609200900</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>JPIYM</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>RIVER KWAI INTERNATIONAL FOOD INDUSTRY CO., LTD.</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>SWEET CORN</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>RESIN-PALLET,NO RED WALL CONTAINER,CLEAN CONTAINER NO OIL STAINS , NO RUSTY ,NO CUT OR HOLE</t>
+          <t>Good and Clean Container (Food Grade)
+(No leaks, no odors, and no oil stains.)</t>
         </is>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
@@ -1600,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="4">
         <f>SUM(M9:U9)-V9</f>
@@ -1646,25 +1647,25 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900108</t>
+          <t>HASLS22260900267</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>202609241200</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n"/>
+          <t>202609211200</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1672,12 +1673,12 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1687,27 +1688,27 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>YEARRAKARN CO., LTD.</t>
+          <t>SCG (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>NON-DAIRY CERAMER</t>
+          <t>VALVE</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>FOOD GRADE CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>0</v>
@@ -1777,66 +1778,62 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900113</t>
+          <t>HASLS22260900268</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>202609271400</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>THSRP</t>
-        </is>
-      </c>
+          <t>202609230900</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>RIVER KWAI INTERNATIONAL FOOD INDUSTRY CO., LTD.</t>
+          <t>SCG (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>CANNED SWEET CORN</t>
+          <t>VALVE</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>REQUEST CLEAN CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1912,12 +1909,12 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900142</t>
+          <t>HASLS22260900421</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1927,10 +1924,10 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>202609211000</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n"/>
+          <t>202609271700</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1938,27 +1935,27 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>JPSDJ</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>K-MUCH INDUSTRY CO.,LTD.</t>
+          <t>GIMSAN INTERNATIONAL CO.,LTD.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>ANIMAL FEED</t>
+          <t>OTC MEDICINE</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1967,13 +1964,13 @@
         </is>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>0</v>
@@ -2043,25 +2040,25 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900183</t>
+          <t>HASLS22260900447</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>KUS</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>202609222100</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n"/>
+          <t>202609211200</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -2069,42 +2066,42 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>JPMIZ</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x30 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>20260912</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>THAI QUALITY STARCH CO.,LTD.</t>
+          <t>R&amp;B FOOD SUPPLY PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>NATIVE TAPIOCA STARCH</t>
+          <t>BREADCRUMB</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>REQUEST FOOD GRADE / SMOOTH FLOOR / N O SMELL / UNDER DECK</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
@@ -2125,10 +2122,10 @@
         <v>0</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X13" s="4">
         <f>SUM(M13:U13)-V13</f>
@@ -2174,25 +2171,25 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900236</t>
+          <t>HASLS22260900489</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n"/>
+          <t>202609230900</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -2200,7 +2197,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -2210,23 +2207,22 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>RIVER KWAI INTERNATIONAL FOOD INDUSTRY CO., LTD.</t>
+          <t>SMS CORPORATION CO., LTD.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>SWEET CORN</t>
+          <t>MODIFIED TAPIOCA STARCH  SWP-0555-26</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>Good and Clean Container (Food Grade)
-(No leaks, no odors, and no oil stains.)</t>
+          <t>NEED VERY CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M14" s="4" t="n">
@@ -2306,38 +2302,42 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900267</t>
+          <t>HASLS22260900527</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>202609211000</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
+          <t>202609270600</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>THSRP</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -2347,21 +2347,21 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>SCG (THAILAND) CO., LTD.</t>
+          <t>SMS CORPORATION CO., LTD.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>VALVE</t>
+          <t>MODIFIED TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>FOOD GRADE CONTAINER / DO NOT RELEAESE RED WALL CONTAINER</t>
         </is>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>0</v>
@@ -2437,25 +2437,25 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900421</t>
+          <t>HASLS22260900541</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>PGPO</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>202609271700</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n"/>
+          <t>202610131500</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -2463,12 +2463,12 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>GIMSAN INTERNATIONAL CO.,LTD.</t>
+          <t>UENO FINE CHEMICALS INDUSTRY (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>OTC MEDICINE</t>
+          <t>MALTITOL SYRUP</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -2568,25 +2568,25 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900505</t>
+          <t>HASLS22260900591</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>0151N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>202609191900</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n"/>
+          <t>202610191500</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -2594,36 +2594,36 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x25 </t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>KITZ (THAILAND) LTD</t>
+          <t>DP WORLD LOGISTICS SOLUTIONS (THAILAND) COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>VALVE</t>
+          <t>SOYBEAN OIL</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>Request good and clean container</t>
+          <t>**DO NOT RELEASE CNTR WAIT APPROVE** *FLEXIBAG* SERVEY 2026-10-12</t>
         </is>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -2699,66 +2699,62 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900527</t>
+          <t>HASLS22260900729</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>202609271400</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>THSRP</t>
-        </is>
-      </c>
+          <t>202609211200</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>SMS CORPORATION CO., LTD.</t>
+          <t>APEX CIRCUIT (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>MODIFIED TAPIOCA STARCH</t>
+          <t>PRINTED CIRCUIT BOARD</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>FOOD GRADE CONTAINER / DO NOT RELEAESE RED WALL CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -2834,25 +2830,25 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900541</t>
+          <t>HASLS22260900731</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>202610131500</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n"/>
+          <t>202609211200</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -2865,22 +2861,22 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>UENO FINE CHEMICALS INDUSTRY (THAILAND) LTD.</t>
+          <t>APEX CIRCUIT (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>MALTITOL SYRUP</t>
+          <t>PRINTED CIRCUIT BOARD</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2889,13 +2885,13 @@
         </is>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>0</v>
@@ -2965,25 +2961,25 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900591</t>
+          <t>HASLS22260900732</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>202610191500</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n"/>
+          <t>202609211200</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -2991,42 +2987,42 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x25 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>20260912</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>DP WORLD LOGISTICS SOLUTIONS (THAILAND) COMPANY LIMITED</t>
+          <t>APEX CIRCUIT (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>SOYBEAN OIL</t>
+          <t>PRINTED CIRCUIT BOARD</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>**DO NOT RELEASE CNTR WAIT APPROVE** *FLEXIBAG* SERVEY 2026-10-12</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>0</v>
@@ -3111,10 +3107,10 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>202610101900</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n"/>
+          <t>202610110800</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -3350,7 +3346,7 @@
         <v>19</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1">
@@ -3363,7 +3359,7 @@
         <v>19</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
+++ b/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
@@ -499,15 +499,15 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">
@@ -600,47 +600,47 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>GP22 Remaining</t>
+          <t>GP22</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>GP42 Remaining</t>
+          <t>GP42</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>GP45 Remaining</t>
+          <t>GP45</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>RE22 Remaining</t>
+          <t>RE22</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>RE45 Remaining</t>
+          <t>RE45</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>UT22 Remaining</t>
+          <t>UT22</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>UT42 Remaining</t>
+          <t>UT42</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>PC22 Remaining</t>
+          <t>PC22</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>PC42 Remaining</t>
+          <t>PC42</t>
         </is>
       </c>
     </row>

--- a/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
+++ b/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$U$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$U$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -662,10 +662,10 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>202609230900</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n"/>
+          <t>202609221300</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="M3" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N3" s="4" t="n">
         <v>0</v>
@@ -747,10 +747,10 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>202609211200</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n"/>
+          <t>202609211300</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="M4" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>0</v>
@@ -817,72 +817,68 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802514</t>
+          <t>HASLS22260802334</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>202609270600</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>THSRP</t>
-        </is>
-      </c>
+          <t>202609211300</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x6 </t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>TOYOX ASIA (THAILAND) CO., LTD.</t>
+          <t>SUKASAEM WATTANA CO.,LTD.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>TOYOX PRESSURE HOSES</t>
+          <t>TILE ADHESIVE AND TILE GROUT</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>REQ. GOOD AND CLEAN CONTAINER</t>
+          <t>RQS CLEAN &amp; GOOD CONTAINER CONDITION.</t>
         </is>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="4" t="n">
         <v>0</v>
@@ -906,25 +902,25 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802581</t>
+          <t>HASLS22260802405</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>202609222100</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n"/>
+          <t>202609240200</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -932,7 +928,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -942,22 +938,22 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CHANG YI TRADING CO.,L TD</t>
+          <t>THAI PRESIDENT FOODS PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOODSTUFFS </t>
+          <t>INSTANT NOODLES</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>REUQEST CONTIANER GOOD CONDITION FOR FOODSTUFF</t>
+          <t>REQUEST CLEAN AND FOOD GRADE CONTAINER ONLY</t>
         </is>
       </c>
       <c r="M6" s="4" t="n">
@@ -1006,10 +1002,10 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>202609241200</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n"/>
+          <t>202609240200</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1091,10 +1087,10 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>202609241200</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n"/>
+          <t>202609240200</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1161,25 +1157,25 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900236</t>
+          <t>HASLS22260900195</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>202609200900</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n"/>
+          <t>202609221300</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1187,37 +1183,36 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPSEN</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x6 </t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>RIVER KWAI INTERNATIONAL FOOD INDUSTRY CO., LTD.</t>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>SWEET CORN</t>
+          <t>TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Good and Clean Container (Food Grade)
-(No leaks, no odors, and no oil stains.)</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1247,25 +1242,25 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900267</t>
+          <t>HASLS22260900196</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>202609211200</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n"/>
+          <t>202609221300</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1273,27 +1268,27 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPSEN</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x12 </t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>SCG (THAILAND) CO., LTD.</t>
+          <t>SANGUAN WONGSE STARCH CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>VALVE</t>
+          <t>TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1347,10 +1342,10 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>202609230900</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n"/>
+          <t>202609221300</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1417,25 +1412,25 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900421</t>
+          <t>HASLS22260900304</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>202609271700</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n"/>
+          <t>202609221300</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1443,27 +1438,27 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>GIMSAN INTERNATIONAL CO.,LTD.</t>
+          <t>TRUE LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>OTC MEDICINE</t>
+          <t>ANIMAL MEDICINE</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1472,13 +1467,13 @@
         </is>
       </c>
       <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>0</v>
@@ -1502,25 +1497,25 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900447</t>
+          <t>HASLS22260900386</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>202609211200</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n"/>
+          <t>202609240200</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1528,42 +1523,42 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>R&amp;B FOOD SUPPLY PUBLIC COMPANY LIMITED</t>
+          <t>UNICORD PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>BREADCRUMB</t>
+          <t>CANNED GOODS</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Clean container for food stuff with strong board (without extra charge)</t>
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
@@ -1587,25 +1582,25 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900489</t>
+          <t>HASLS22260900421</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>202609230900</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n"/>
+          <t>202609290000</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1613,7 +1608,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1623,22 +1618,22 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>SMS CORPORATION CO., LTD.</t>
+          <t>GIMSAN INTERNATIONAL CO.,LTD.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>MODIFIED TAPIOCA STARCH  SWP-0555-26</t>
+          <t>OTC MEDICINE</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>NEED VERY CLEAN CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M14" s="4" t="n">
@@ -1672,62 +1667,58 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900527</t>
+          <t>HASLS22260900541</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>PGPO</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>202609270600</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>THSRP</t>
-        </is>
-      </c>
+          <t>202610131430</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x4 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>SMS CORPORATION CO., LTD.</t>
+          <t>UENO FINE CHEMICALS INDUSTRY (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>MODIFIED TAPIOCA STARCH</t>
+          <t>MALTITOL SYRUP</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>FOOD GRADE CONTAINER / DO NOT RELEAESE RED WALL CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M15" s="4" t="n">
@@ -1761,25 +1752,25 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900541</t>
+          <t>HASLS22260900591</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>202610131500</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n"/>
+          <t>202610191500</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1787,36 +1778,36 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x25 </t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>UENO FINE CHEMICALS INDUSTRY (THAILAND) LTD.</t>
+          <t>DP WORLD LOGISTICS SOLUTIONS (THAILAND) COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>MALTITOL SYRUP</t>
+          <t>SOYBEAN OIL</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>**DO NOT RELEASE CNTR WAIT APPROVE** *FLEXIBAG* SERVEY 2026-10-12</t>
         </is>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1846,25 +1837,25 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900591</t>
+          <t>HASLS22260901039</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>202610191500</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n"/>
+          <t>202610110800</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -1872,42 +1863,42 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>JPMYJ</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x25 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>20260912</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>DP WORLD LOGISTICS SOLUTIONS (THAILAND) COMPANY LIMITED</t>
+          <t>PERFECT COMPANION GROUP CO., LTD.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>SOYBEAN OIL</t>
+          <t>PET FOOD</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>**DO NOT RELEASE CNTR WAIT APPROVE** *FLEXIBAG* SERVEY 2026-10-12</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M17" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
@@ -1931,62 +1922,66 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900729</t>
+          <t>HASLS22260901062</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>202609211200</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n"/>
+          <t>202609270600</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>THSRP</t>
+        </is>
+      </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>APEX CIRCUIT (THAILAND) CO., LTD.</t>
+          <t>SMS CORPORATION CO., LTD.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>PRINTED CIRCUIT BOARD</t>
+          <t xml:space="preserve">MODIFIED TAPIOCA STARCH </t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>NEED VERY CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -2016,12 +2011,12 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900731</t>
+          <t>HASLS22260901491</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2031,10 +2026,10 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>202609211200</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n"/>
+          <t>202610171300</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>THBKK</t>
@@ -2047,31 +2042,31 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>APEX CIRCUIT (THAILAND) CO., LTD.</t>
+          <t>UCHIYAMA(THAILAND)CO.,LTD.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>PRINTED CIRCUIT BOARD</t>
+          <t>SPARE PART</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQ CLEAN CONTAINER AND GRADE A</t>
         </is>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0</v>
@@ -2099,274 +2094,104 @@
       </c>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900732</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>202609211200</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>20260916</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>APEX CIRCUIT (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>PRINTED CIRCUIT BOARD</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="4" t="n">
-        <v>0</v>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5">
+        <f>SUM(M3:M19)</f>
+        <v/>
+      </c>
+      <c r="N20" s="5">
+        <f>SUM(N3:N19)</f>
+        <v/>
+      </c>
+      <c r="O20" s="5">
+        <f>SUM(O3:O19)</f>
+        <v/>
+      </c>
+      <c r="P20" s="5">
+        <f>SUM(P3:P19)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="5">
+        <f>SUM(Q3:Q19)</f>
+        <v/>
+      </c>
+      <c r="R20" s="5">
+        <f>SUM(R3:R19)</f>
+        <v/>
+      </c>
+      <c r="S20" s="5">
+        <f>SUM(S3:S19)</f>
+        <v/>
+      </c>
+      <c r="T20" s="5">
+        <f>SUM(T3:T19)</f>
+        <v/>
+      </c>
+      <c r="U20" s="5">
+        <f>SUM(U3:U19)</f>
+        <v/>
       </c>
     </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260901039</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>DJCF</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>0152N</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>202610110800</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>JPMYJ</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>20260905</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>PERFECT COMPANION GROUP CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>PET FOOD</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>0</v>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
-    <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5">
-        <f>SUM(M3:M21)</f>
-        <v/>
-      </c>
-      <c r="N22" s="5">
-        <f>SUM(N3:N21)</f>
-        <v/>
-      </c>
-      <c r="O22" s="5">
-        <f>SUM(O3:O21)</f>
-        <v/>
-      </c>
-      <c r="P22" s="5">
-        <f>SUM(P3:P21)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="5">
-        <f>SUM(Q3:Q21)</f>
-        <v/>
-      </c>
-      <c r="R22" s="5">
-        <f>SUM(R3:R21)</f>
-        <v/>
-      </c>
-      <c r="S22" s="5">
-        <f>SUM(S3:S21)</f>
-        <v/>
-      </c>
-      <c r="T22" s="5">
-        <f>SUM(T3:T21)</f>
-        <v/>
-      </c>
-      <c r="U22" s="5">
-        <f>SUM(U3:U21)</f>
-        <v/>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Smart Logistics Service (Thailand ) Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="13" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Smart Logistics Service (Thailand ) Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" ht="13" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>62</v>
+      <c r="B25" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:U21"/>
+  <autoFilter ref="A2:U19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:U1"/>
   </mergeCells>

--- a/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
+++ b/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
@@ -487,27 +487,27 @@
   <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="5" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">

--- a/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
+++ b/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
@@ -478,7 +478,7 @@
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
@@ -607,22 +607,22 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260800029</t>
+          <t>HASLS22260801961</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610151300</t>
+          <t>202610191500</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -643,7 +643,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -692,22 +692,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802336</t>
+          <t>HASLS22260900541</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>PGPO</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610080800</t>
+          <t>202610150100</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -718,42 +718,42 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>NMB-MINEBEA THAI LTD.</t>
+          <t>UENO FINE CHEMICALS INDUSTRY (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>BALL BEARING</t>
+          <t>MALTITOL SYRUP</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>REQUEST CLEAN CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>0</v>
@@ -777,22 +777,22 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802353</t>
+          <t>HASLS22260900554</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610080800</t>
+          <t>202610110500</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -813,22 +813,23 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>VARA FOOD &amp; DRINK CO., LTD.</t>
+          <t>PANTAINORASINGH MANUFACTURER CO.,LTD.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>CANNED GOODS</t>
+          <t>FOODSTUFFS</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>REQUEST : CLEAN CONTAINER, NO RUST</t>
+          <t>Please notify us of the first day of return of the container free of charge.
+The container must be used for food storage, be in new condition, clean,</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -862,22 +863,22 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900541</t>
+          <t>HASLS22260900591</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202610150100</t>
+          <t>202610191500</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -888,36 +889,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x25 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>UENO FINE CHEMICALS INDUSTRY (THAILAND) LTD.</t>
+          <t>DP WORLD LOGISTICS SOLUTIONS (THAILAND) COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>MALTITOL SYRUP</t>
+          <t>SOYBEAN OIL</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONTAINER</t>
+          <t>**APPROVAL BY MR.SANGJUN KIM DD.23/09/2026** *FLEXIBAG* SERVEY 2026-10-12</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -947,22 +948,22 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900586</t>
+          <t>HASLS22260900657</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>202610071530</t>
+          <t>202610151200</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -973,42 +974,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx10 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>BIRLA CARBON (THAILAND) PUBLIC COMPANY LIMITED</t>
+          <t>WIDE WATER GATE CO.,LTD</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>CABON BLACK</t>
+          <t>ALOE VERA GEL SAPS</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Clean container / No rust / No hole / No sharp surface inside areas in container</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>0</v>
@@ -1032,22 +1033,22 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900591</t>
+          <t>HASLS22260900835</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610190500</t>
+          <t>202610110500</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1058,36 +1059,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x25 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20260912</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>DP WORLD LOGISTICS SOLUTIONS (THAILAND) COMPANY LIMITED</t>
+          <t>LOGTHAI-OROTEX CO,LTD</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>SOYBEAN OIL</t>
+          <t>RUBBER PARTS</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>**APPROVAL BY MR.SANGJUN KIM DD.23/09/2026** *FLEXIBAG* SERVEY 2026-10-12</t>
+          <t>Request good and clean container , not damage , none any hole , smooth floor , ceiling &amp; wall not deforme</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1117,22 +1118,22 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900734</t>
+          <t>HASLS22260901039</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202610071530</t>
+          <t>202610110500</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1143,32 +1144,32 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPMYJ</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>OTANI RADIAL CO., LTD.</t>
+          <t>PERFECT COMPANION GROUP CO., LTD.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>NEW TIRE</t>
+          <t>PET FOOD</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD AND CLEAN CONTAINER</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
@@ -1178,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>0</v>
@@ -1202,22 +1203,22 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900826</t>
+          <t>HASLS22260901077</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202610080800</t>
+          <t>202610062230</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -1228,42 +1229,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>ROFU (THAILAND) LTD.</t>
+          <t>SIAM FUKOKU CO.,LTD.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>SHOE</t>
+          <t>BLADE RUBBER</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>RQS CLEAN &amp; GOOD CONTAINER CONDITION.</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>0</v>
@@ -1287,22 +1288,22 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901024</t>
+          <t>HASLS22260901166</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610071530</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1313,17 +1314,17 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>RUVVO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1333,22 +1334,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>BEER ALC 5%</t>
+          <t>SODA WATER</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONTAINER</t>
+          <t>REQ under desk cargo and food grade container</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>0</v>
@@ -1372,22 +1373,22 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901036</t>
+          <t>HASLS22260901191</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>202610071530</t>
+          <t>202610110500</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1398,42 +1399,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx8 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>KANGWAL POLYESTER CO., LTD.</t>
+          <t>I-TAIL CORPORATION PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>POLYESTER</t>
+          <t>PET FOOD</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1X40'HQ CY AT SMART / 7X40'HQ CY AT B.C.</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -1457,22 +1458,22 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901121</t>
+          <t>HASLS22260901354</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>202610080800</t>
+          <t>202610110500</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1483,7 +1484,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>RUVVO</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1493,22 +1494,22 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>THAI AGRI FOODS PUBLIC COMPANY LIMITED</t>
+          <t>ORIENTAL FOODS LIMITED PARTNERSHIP</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>SWEET CHILLI SAUCE FOR CHICKEN</t>
+          <t>RICE STICK</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONTAINER</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
@@ -1542,22 +1543,22 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901491</t>
+          <t>HASLS22260901358</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>202610220400</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1568,32 +1569,32 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>UCHIYAMA(THAILAND)CO.,LTD.</t>
+          <t>FRUIT ORGANIC CO., LTD.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>SPARE PART</t>
+          <t>SNACK</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>REQ CLEAN CONTAINER AND GRADE A</t>
+          <t>CLEAN AND GRADE A CTNR</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
@@ -1603,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>0</v>
@@ -1627,12 +1628,12 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901581</t>
+          <t>HASLS22260901418</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWRG</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1642,47 +1643,51 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>202610071530</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>202610141700</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>THSRP</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>AJINOMOTO CO., (THAILAND) LTD.</t>
+          <t>SMS CORPORATION CO., LTD.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>AJITIDE I+G</t>
+          <t>MODIFIED TAPIOCA STARCH</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>PLS ARRANGE GRADE A CONTAINER FOR FOODSTUFF PRODUCT WITH 6 RINGS IN ORDER TO HOOK NET IN THE CONTAINER.</t>
+          <t>FOOD GRADE CONTAINER / DO NOT RELEASE RED WALL CONTAINER</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1712,12 +1717,12 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902809</t>
+          <t>HASLS22260901491</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1727,7 +1732,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202610060900</t>
+          <t>202610221330</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1738,36 +1743,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>SS EXCELLENT NETWORK CO.,LTD</t>
+          <t>UCHIYAMA(THAILAND)CO.,LTD.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>COPPER INGOT</t>
+          <t>SPARE PART</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>RQST CONTAINER 32.5 TONS .</t>
+          <t>REQ CLEAN CONTAINER AND GRADE A</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1875,7 +1880,7 @@
         <v>14</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1">
@@ -1888,7 +1893,7 @@
         <v>14</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
+++ b/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U118"/>
+  <dimension ref="A1:U117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -707,7 +707,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261017</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202610151500</t>
+          <t>202610152100</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610151500</t>
+          <t>202610152100</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>202610290800</t>
+          <t>202610301400</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>202610201300</t>
+          <t>202610170100</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2227,22 +2227,22 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900365</t>
+          <t>HASLS22260900420</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202610110500</t>
+          <t>202610200200</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -2253,42 +2253,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>ASIA-PACIFIC LOGISTICS CO., LTD.</t>
+          <t>V.THAI FOOD PRODUCT CO.,LTD.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>BISCUITS</t>
+          <t>SAUCE</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>FOOD GRADE &amp; CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="2" t="n">
         <v>0</v>
@@ -2312,22 +2312,22 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900420</t>
+          <t>HASLS22260900514</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202610200200</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2348,22 +2348,22 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261010</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>V.THAI FOOD PRODUCT CO.,LTD.</t>
+          <t>BANGKOK STARCH INDUSTRIAL CO., LTD.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>SAUCE</t>
+          <t xml:space="preserve">STARCH </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>FOOD GRADE &amp; CLEAN CONTAINER</t>
+          <t>CONTAINER : PLS. RELEASE CTNR FOOD GRADE CONDITION ( FOR LOADING FOODS ) ONLY.</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
@@ -2397,22 +2397,22 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900514</t>
+          <t>HASLS22260900541</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>PGPO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610152300</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -2423,36 +2423,36 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>BANGKOK STARCH INDUSTRIAL CO., LTD.</t>
+          <t>UENO FINE CHEMICALS INDUSTRY (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STARCH </t>
+          <t>MALTITOL SYRUP</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>CONTAINER : PLS. RELEASE CTNR FOOD GRADE CONDITION ( FOR LOADING FOODS ) ONLY.</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2482,12 +2482,12 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900524</t>
+          <t>HASLS22260900554</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610202130</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2508,36 +2508,37 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>AQUACULTURE PROMOTION CO., LTD.</t>
+          <t>PANTAINORASINGH MANUFACTURER CO.,LTD.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>PREMIX</t>
+          <t>FOODSTUFFS</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>GRADE A  CONTANER</t>
+          <t>Please notify us of the first day of return of the container free of charge.
+The container must be used for food storage, be in new condition, clean,</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2567,22 +2568,22 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900541</t>
+          <t>HASLS22260900557</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>202610150100</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -2593,36 +2594,36 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPKIJ</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>UENO FINE CHEMICALS INDUSTRY (THAILAND) LTD.</t>
+          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>MALTITOL SYRUP</t>
+          <t>FLOURS</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Container Grade A</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2652,22 +2653,22 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900554</t>
+          <t>HASLS22260900561</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>202610110500</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2678,37 +2679,36 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>JPKIJ</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>PANTAINORASINGH MANUFACTURER CO.,LTD.</t>
+          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>FOODSTUFFS</t>
+          <t>FLOURS</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Please notify us of the first day of return of the container free of charge.
-The container must be used for food storage, be in new condition, clean,</t>
+          <t>Container Grade A,</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2738,22 +2738,22 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900557</t>
+          <t>HASLS22260900562</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>JPKIJ</t>
+          <t>JPMYJ</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2823,22 +2823,22 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900561</t>
+          <t>HASLS22260900591</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>202610212100</t>
+          <t>202610191500</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2849,36 +2849,36 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>JPKIJ</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x25 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
+          <t>DP WORLD LOGISTICS SOLUTIONS (THAILAND) COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>FLOURS</t>
+          <t>SOYBEAN OIL</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Container Grade A,</t>
+          <t>**APPROVAL BY MR.SANGJUN KIM DD.23/09/2026** *FLEXIBAG* SERVEY 2026-10-12</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
@@ -2908,22 +2908,22 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900562</t>
+          <t>HASLS22260900618</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>202610212100</t>
+          <t>202610200200</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>JPMYJ</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2944,22 +2944,22 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
+          <t>V.THAI FOOD PRODUCT CO.,LTD.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>FLOURS</t>
+          <t>SAUCE</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Container Grade A</t>
+          <t>FOOD GRADE &amp; CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
@@ -2993,22 +2993,22 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900591</t>
+          <t>HASLS22260900619</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202610191500</t>
+          <t>202610301400</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3019,36 +3019,36 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x25 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20260912</t>
+          <t>20261024</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>DP WORLD LOGISTICS SOLUTIONS (THAILAND) COMPANY LIMITED</t>
+          <t>V.THAI FOOD PRODUCT CO.,LTD.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>SOYBEAN OIL</t>
+          <t>SAUCE</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>**APPROVAL BY MR.SANGJUN KIM DD.23/09/2026** *FLEXIBAG* SERVEY 2026-10-12</t>
+          <t>FOOD GRADE &amp; CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>0</v>
@@ -3078,22 +3078,22 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900618</t>
+          <t>HASLS22260900620</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>202610200200</t>
+          <t>202610291300</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3114,22 +3114,22 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261023</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>V.THAI FOOD PRODUCT CO.,LTD.</t>
+          <t>VET SUPERIOR CONSULTANT CO., LTD.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>SAUCE</t>
+          <t>WATER TREATMENT &amp; FEED SUPPLEMENT</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>FOOD GRADE &amp; CLEAN CONTAINER</t>
+          <t>GOOD CONTAINER</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
@@ -3163,33 +3163,37 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900619</t>
+          <t>HASLS22260900631</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>202610290800</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
+          <t>202610191200</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>THLKR</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3199,7 +3203,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20261024</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3214,7 +3218,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>FOOD GRADE &amp; CLEAN CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
@@ -3248,22 +3252,22 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900620</t>
+          <t>HASLS22260900641</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>202610280100</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -3274,42 +3278,42 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPIMI</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20261023</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>VET SUPERIOR CONSULTANT CO., LTD.</t>
+          <t>ASE CO., LTD.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>WATER TREATMENT &amp; FEED SUPPLEMENT</t>
+          <t>furniture sofa set</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>GOOD CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P33" s="2" t="n">
         <v>0</v>
@@ -3333,37 +3337,33 @@
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900631</t>
+          <t>HASLS22260900653</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>202610182100</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>THLKR</t>
-        </is>
-      </c>
+          <t>202610121900</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3373,17 +3373,17 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>V.THAI FOOD PRODUCT CO.,LTD.</t>
+          <t>TOYO SEIKAN (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>SAUCE</t>
+          <t>DYDO BLEND</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3422,22 +3422,22 @@
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900641</t>
+          <t>HASLS22260900654</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>202610121900</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -3448,27 +3448,27 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>JPIMI</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>ASE CO., LTD.</t>
+          <t>TOYO SEIKAN (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>940161</t>
+          <t>DYDO BLEND</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" s="2" t="n">
         <v>0</v>
@@ -3507,22 +3507,22 @@
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900653</t>
+          <t>HASLS22260900656</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>202610121900</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3592,22 +3592,22 @@
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900654</t>
+          <t>HASLS22260900657</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -3618,27 +3618,27 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>TOYO SEIKAN (THAILAND) CO., LTD.</t>
+          <t>WIDE WATER GATE CO.,LTD</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>DYDO BLEND</t>
+          <t>ALOE VERA GEL SAPS</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0</v>
@@ -3677,22 +3677,22 @@
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900656</t>
+          <t>HASLS22260900660</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -3703,42 +3703,42 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPKIJ</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>TOYO SEIKAN (THAILAND) CO., LTD.</t>
+          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>DYDO BLEND</t>
+          <t>FLOURS</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Container Grade A, Underdeck</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>0</v>
@@ -3762,22 +3762,22 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900657</t>
+          <t>HASLS22260900661</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -3788,27 +3788,27 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>JPKCZ</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261017</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>WIDE WATER GATE CO.,LTD</t>
+          <t>HYMOLD (THAILAND) LIMITED</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>ALOE VERA GEL SAPS</t>
+          <t>FERRO SILICON MAGNESIUM</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N39" s="2" t="n">
         <v>0</v>
@@ -3847,22 +3847,22 @@
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900660</t>
+          <t>HASLS22260900664</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610241500</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -3878,12 +3878,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3898,17 +3898,17 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Container Grade A, Underdeck</t>
+          <t>Container Grade A</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" s="2" t="n">
         <v>0</v>
@@ -3932,22 +3932,22 @@
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900661</t>
+          <t>HASLS22260900665</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610241500</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>JPKCZ</t>
+          <t>JPMYJ</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3968,22 +3968,22 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20261017</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>HYMOLD (THAILAND) LIMITED</t>
+          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>FERRO SILICON MAGNESIUM</t>
+          <t>FLOURS</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Container Grade A</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
@@ -4017,22 +4017,22 @@
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900664</t>
+          <t>HASLS22260900757</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>202610241500</t>
+          <t>202610191500</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -4043,42 +4043,42 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>JPKIJ</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
+          <t>R.J. LONDON CHEMICAL INDUSTRIES CO., LTD.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>FLOURS</t>
+          <t>AUTO ACCESSORIES</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Container Grade A</t>
+          <t>REQUEST GOOD CONTAINER,NO LEAK,NO SCRATCHES,NO OIL, BECAUSE PRODUCT IN CARTON NO PALLET.</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P42" s="2" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900665</t>
+          <t>HASLS22260900770</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>202610241500</t>
+          <t>202610291300</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>JPMYJ</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -4138,22 +4138,22 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
+          <t>SITTHINAN CO., LTD.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>FLOURS</t>
+          <t>NATIVE MUNG BEAN STARCH</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Container Grade A</t>
+          <t>REQUEST A-GRADE, FOOD GRADE CLEAN AND GOOD CONTAINER</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
@@ -4187,22 +4187,22 @@
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900757</t>
+          <t>HASLS22260900779</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>202610191500</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -4213,42 +4213,43 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>R.J. LONDON CHEMICAL INDUSTRIES CO., LTD.</t>
+          <t>RIVER KWAI INTERNATIONAL FOOD INDUSTRY CO., LTD.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>AUTO ACCESSORIES</t>
+          <t>SWEET CORN</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD CONTAINER,NO LEAK,NO SCRATCHES,NO OIL, BECAUSE PRODUCT IN CARTON NO PALLET.</t>
+          <t>Good and clean Container (Food Grade)
+(No leaks, no odors, and no oil stains.)</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P44" s="2" t="n">
         <v>0</v>
@@ -4272,22 +4273,22 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900770</t>
+          <t>HASLS22260900783</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>202610280100</t>
+          <t>202611011600</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -4298,7 +4299,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -4308,22 +4309,23 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>SITTHINAN CO., LTD.</t>
+          <t>RIVER KWAI INTERNATIONAL FOOD INDUSTRY CO., LTD.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>NATIVE MUNG BEAN STARCH</t>
+          <t>SWEET CORN</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>REQUEST A-GRADE, FOOD GRADE CLEAN AND GOOD CONTAINER</t>
+          <t>Good and clean Container (Food Grade)
+(No leaks, no odors, and no oil stains.)</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
@@ -4357,7 +4359,7 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900779</t>
+          <t>HASLS22260900814</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4372,7 +4374,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -4393,23 +4395,22 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>RIVER KWAI INTERNATIONAL FOOD INDUSTRY CO., LTD.</t>
+          <t>SOJITZ (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>SWEET CORN</t>
+          <t>CANNED COCONUT MILK</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Good and clean Container (Food Grade)
-(No leaks, no odors, and no oil stains.)</t>
+          <t>**REQ : Container dry and clean, no rust, no oil, no hole, no bur, no smell and wooden floor.</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
@@ -4443,22 +4444,22 @@
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900783</t>
+          <t>HASLS22260900835</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>202611011600</t>
+          <t>202610110500</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -4469,7 +4470,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4479,23 +4480,22 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>RIVER KWAI INTERNATIONAL FOOD INDUSTRY CO., LTD.</t>
+          <t>LOGTHAI-OROTEX CO,LTD</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>SWEET CORN</t>
+          <t>RUBBER PARTS</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Good and clean Container (Food Grade)
-(No leaks, no odors, and no oil stains.)</t>
+          <t>Request good and clean container , not damage , none any hole , smooth floor , ceiling &amp; wall not deforme</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
@@ -4529,12 +4529,12 @@
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900814</t>
+          <t>HASLS22260900860</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610241500</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4565,22 +4565,22 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>SOJITZ (THAILAND) CO., LTD.</t>
+          <t>THAI MARSOL CO., LTD.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>CANNED COCONUT MILK</t>
+          <t xml:space="preserve">PAPER LAMINATED </t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>**REQ : Container dry and clean, no rust, no oil, no hole, no bur, no smell and wooden floor.</t>
+          <t>REQUEST GOOD &amp; CLEAN CONTAINER ( CONTAINER GRADE A+++)</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
@@ -4614,22 +4614,22 @@
     <row r="49" ht="13" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900835</t>
+          <t>HASLS22260900867</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>202610110500</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -4645,37 +4645,37 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>LOGTHAI-OROTEX CO,LTD</t>
+          <t>R.J. LONDON CHEMICAL INDUSTRIES CO., LTD.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>RUBBER PARTS</t>
+          <t>AUTO ACCESSORIES</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Request good and clean container , not damage , none any hole , smooth floor , ceiling &amp; wall not deforme</t>
+          <t>REQUEST GOOD CONTAINER,NO LEAK,NO RUST,NO SCRATCHES,NO OIL,  BECAUSE PRODUCT IN CARTON NO PALLET.</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P49" s="2" t="n">
         <v>0</v>
@@ -4699,22 +4699,22 @@
     <row r="50" ht="13" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900860</t>
+          <t>HASLS22260900868</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>202610241500</t>
+          <t>202610291300</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -4740,27 +4740,27 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>THAI MARSOL CO., LTD.</t>
+          <t>R.J. LONDON CHEMICAL INDUSTRIES CO., LTD.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAPER LAMINATED </t>
+          <t>AUTO ACCESSORIES</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD &amp; CLEAN CONTAINER ( CONTAINER GRADE A+++)</t>
+          <t>REQUEST GOOD CONTAINER,NO LEAK,NO RUST,NO SCRATCHES,NO OIL,  BECAUSE PRODUCT IN CARTON NO PALLET.</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P50" s="2" t="n">
         <v>0</v>
@@ -4784,22 +4784,22 @@
     <row r="51" ht="13" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900867</t>
+          <t>HASLS22260900904</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>202610212100</t>
+          <t>202610152100</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -4810,36 +4810,36 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>RUVVO</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>R.J. LONDON CHEMICAL INDUSTRIES CO., LTD.</t>
+          <t>TAVEEPHOL PRODUCT CO.,LTD.</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>AUTO ACCESSORIES</t>
+          <t>ASSORTED FLAVOUR DRINK</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD CONTAINER,NO LEAK,NO RUST,NO SCRATCHES,NO OIL,  BECAUSE PRODUCT IN CARTON NO PALLET.</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="2" t="n">
         <v>0</v>
@@ -4869,22 +4869,22 @@
     <row r="52" ht="13" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900868</t>
+          <t>HASLS22260900914</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>PGPO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>202610280100</t>
+          <t>202610150800</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -4895,42 +4895,42 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPTMK</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261010</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>R.J. LONDON CHEMICAL INDUSTRIES CO., LTD.</t>
+          <t>ASIA MODIFIED STARCH CO., LTD.</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>AUTO ACCESSORIES</t>
+          <t>STARCH</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD CONTAINER,NO LEAK,NO RUST,NO SCRATCHES,NO OIL,  BECAUSE PRODUCT IN CARTON NO PALLET.</t>
+          <t>CONTAINER GRADE A OR FOOD GRADE</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P52" s="2" t="n">
         <v>0</v>
@@ -4954,22 +4954,22 @@
     <row r="53" ht="13" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900904</t>
+          <t>HASLS22260900950</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>202610151500</t>
+          <t>202610241500</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -4980,27 +4980,27 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>RUVVO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>TAVEEPHOL PRODUCT CO.,LTD.</t>
+          <t>SRINANAPORN MARKETING PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>ASSORTED FLAVOUR DRINK</t>
+          <t>FOODSTUFF</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" s="2" t="n">
         <v>0</v>
@@ -5039,22 +5039,22 @@
     <row r="54" ht="13" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900914</t>
+          <t>HASLS22260900960</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>202610150100</t>
+          <t>202610110500</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -5065,36 +5065,36 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>JPTMK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>ASIA MODIFIED STARCH CO., LTD.</t>
+          <t>THAI SIN RUBBER INDUSTRY CO., LTD.</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>STARCH</t>
+          <t>MOTORCYCLE TYRES</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>CONTAINER GRADE A OR FOOD GRADE</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N54" s="2" t="n">
         <v>0</v>
@@ -5124,22 +5124,22 @@
     <row r="55" ht="13" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900950</t>
+          <t>HASLS22260901006</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>202610241500</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -5150,27 +5150,27 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>SRINANAPORN MARKETING PUBLIC COMPANY LIMITED</t>
+          <t>TROPICAL PREMIUM FOODS CO., LTD</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>FOODSTUFF</t>
+          <t>SWEET CORN CANNED</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -5179,13 +5179,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P55" s="2" t="n">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     <row r="56" ht="13" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900960</t>
+          <t>HASLS22260901037</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>THAI SIN RUBBER INDUSTRY CO., LTD.</t>
+          <t>KANGWAL POLYESTER CO., LTD.</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>MOTORCYCLE TYRES</t>
+          <t>POLYESTER</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5264,13 +5264,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P56" s="2" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
     <row r="57" ht="13" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901006</t>
+          <t>HASLS22260901048</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -5320,36 +5320,36 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261010</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>TROPICAL PREMIUM FOODS CO., LTD</t>
+          <t>CHEVRON (THAILAND) LIMITED</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>SWEET CORN CANNED</t>
+          <t>LUBE OIL</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Container condition  GRADE B+ CNTR / CLEAN CNTR WITH GOOD CONDITION / NO SMELL/NODAMAGES / STRONG &amp; SMOOTH FLOOR / NO NAILS / LOAD UNDERDECK</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57" s="2" t="n">
         <v>0</v>
@@ -5379,22 +5379,22 @@
     <row r="58" ht="13" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901037</t>
+          <t>HASLS22260901049</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>202610110500</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -5405,42 +5405,42 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>KANGWAL POLYESTER CO., LTD.</t>
+          <t>CHEVRON (THAILAND) LIMITED</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>POLYESTER</t>
+          <t>LUBE OIL</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Container condition  GRADE B+ CNTR / CLEAN CNTR WITH GOOD CONDITION / NO SMELL/NODAMAGES / STRONG &amp; SMOOTH FLOOR / NO NAILS / LOAD UNDERDECK</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P58" s="2" t="n">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     <row r="59" ht="13" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901048</t>
+          <t>HASLS22260901078</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610110500</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -5500,22 +5500,22 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>CHEVRON (THAILAND) LIMITED</t>
+          <t>SIAM FUKOKU CO.,LTD.</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>LUBE OIL</t>
+          <t>BLADE RUBBER</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Container condition  GRADE B+ CNTR / CLEAN CNTR WITH GOOD CONDITION / NO SMELL/NODAMAGES / STRONG &amp; SMOOTH FLOOR / NO NAILS / LOAD UNDERDECK</t>
+          <t>RQS CLEAN &amp; GOOD CONTAINER CONDITION.</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
@@ -5549,22 +5549,22 @@
     <row r="60" ht="13" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901049</t>
+          <t>HASLS22260901080</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610191500</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -5575,42 +5575,42 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>CHEVRON (THAILAND) LIMITED</t>
+          <t>SIAM FUKOKU CO.,LTD.</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>LUBE OIL</t>
+          <t>BLADE RUBBER</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Container condition  GRADE B+ CNTR / CLEAN CNTR WITH GOOD CONDITION / NO SMELL/NODAMAGES / STRONG &amp; SMOOTH FLOOR / NO NAILS / LOAD UNDERDECK</t>
+          <t>RQS CLEAN &amp; GOOD CONTAINER CONDITION.</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P60" s="2" t="n">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     <row r="61" ht="13" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901078</t>
+          <t>HASLS22260901081</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>202610110500</t>
+          <t>202610291300</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -5665,12 +5665,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261023</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -5689,13 +5689,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="N61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P61" s="2" t="n">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     <row r="62" ht="13" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901079</t>
+          <t>HASLS22260901131</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>KUS</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>202610141100</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5755,22 +5755,22 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>SIAM FUKOKU CO.,LTD.</t>
+          <t>BANGKOK STARCH INDUSTRIAL CO., LTD.</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>BLADE RUBBER</t>
+          <t xml:space="preserve">STARCH </t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>RQS CLEAN &amp; GOOD CONTAINER CONDITION.</t>
+          <t>CONTAINER :  PLS. RELEASE CTNR  FOOD GRADE CONDITION ( FOR LOADING FOODS ) ONLY.</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
@@ -5804,22 +5804,22 @@
     <row r="63" ht="13" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901080</t>
+          <t>HASLS22260901138</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>202610191500</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -5830,42 +5830,42 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>SIAM FUKOKU CO.,LTD.</t>
+          <t>THAI PLASPAC PUBLIC CO.,LTD.</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>BLADE RUBBER</t>
+          <t>PLATIC CAP</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>RQS CLEAN &amp; GOOD CONTAINER CONDITION.</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P63" s="2" t="n">
         <v>0</v>
@@ -5889,12 +5889,12 @@
     <row r="64" ht="13" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901081</t>
+          <t>HASLS22260901156</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>202610280100</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5925,22 +5925,22 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>20261023</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>SIAM FUKOKU CO.,LTD.</t>
+          <t>EQUATOR PURE NATURE CO., LTD</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>BLADE RUBBER</t>
+          <t>CLEANING PRODUCT</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>RQS CLEAN &amp; GOOD CONTAINER CONDITION.</t>
+          <t>REQUEST GOOD AND CLEAN THE CONTAINER</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
@@ -5974,22 +5974,22 @@
     <row r="65" ht="13" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901131</t>
+          <t>HASLS22260901182</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>202610121900</t>
+          <t>202610191500</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -6000,42 +6000,43 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>BANGKOK STARCH INDUSTRIAL CO., LTD.</t>
+          <t>F.M.T. (THAILAND) CO., LTD. (HEAD OFFICE)</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STARCH </t>
+          <t>CALCIUM CARBONATE / HS CODE : 2836.50.90</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>CONTAINER :  PLS. RELEASE CTNR  FOOD GRADE CONDITION ( FOR LOADING FOODS ) ONLY.</t>
+          <t>Survey : 2026-10-12, Pickup : 2026-10-14 
+REQ GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P65" s="2" t="n">
         <v>0</v>
@@ -6059,22 +6060,22 @@
     <row r="66" ht="13" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901138</t>
+          <t>HASLS22260901191</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610110500</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -6085,7 +6086,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -6095,22 +6096,22 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>THAI PLASPAC PUBLIC CO.,LTD.</t>
+          <t>I-TAIL CORPORATION PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>PLATIC CAP</t>
+          <t>PET FOOD</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
@@ -6144,22 +6145,22 @@
     <row r="67" ht="13" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901156</t>
+          <t>HASLS22260901205</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -6170,42 +6171,42 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>EQUATOR PURE NATURE CO., LTD</t>
+          <t>BEER THIP BREWERY (1991) CO., LTD</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>CLEANING PRODUCT</t>
+          <t xml:space="preserve">ROCK MOUNTAIN SODA </t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD AND CLEAN THE CONTAINER</t>
+          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67" s="2" t="n">
         <v>0</v>
@@ -6229,12 +6230,12 @@
     <row r="68" ht="13" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901166</t>
+          <t>HASLS22260901303</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -6244,7 +6245,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>202610121900</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -6255,42 +6256,42 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPIMI</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261010</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>SINGHA WORLDWIDE INTERNATIONAL CO., LTD.</t>
+          <t>WOODWORKS THAI CO., LTD. (1980)</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>SODA WATER</t>
+          <t>FURNITURE (STUDY DESK)</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>REQ under desk cargo and food grade container</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="N68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P68" s="2" t="n">
         <v>0</v>
@@ -6314,22 +6315,22 @@
     <row r="69" ht="13" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901175</t>
+          <t>HASLS22260901323</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>202610151500</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -6340,7 +6341,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -6350,22 +6351,22 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>SIAM SANITARY WARE INDUSTRY CO., LTD.</t>
+          <t>BEER THIP BREWERY (1991) CO., LTD</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>SANITARY WARE</t>
+          <t xml:space="preserve">CHANG SODA WATER </t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
@@ -6399,22 +6400,22 @@
     <row r="70" ht="13" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901182</t>
+          <t>HASLS22260901326</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>202610191500</t>
+          <t>202610202300</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -6425,37 +6426,36 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>F.M.T. (THAILAND) CO., LTD. (HEAD OFFICE)</t>
+          <t>BEER THIP BREWERY (1991) CO., LTD</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>CALCIUM CARBONATE / HS CODE : 2836.50.90</t>
+          <t xml:space="preserve">CHANG SODA WATER </t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Survey : 2026-10-12, Pickup : 2026-10-14 
-REQ GOOD AND CLEAN CONTAINER</t>
+          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70" s="2" t="n">
         <v>0</v>
@@ -6485,22 +6485,22 @@
     <row r="71" ht="13" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901191</t>
+          <t>HASLS22260901328</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>202610110500</t>
+          <t>202610202130</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -6521,22 +6521,22 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261017</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>I-TAIL CORPORATION PUBLIC COMPANY LIMITED</t>
+          <t>BEER THIP BREWERY (1991) CO., LTD</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>PET FOOD</t>
+          <t xml:space="preserve">CHANG SODA WATER </t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
@@ -6570,12 +6570,12 @@
     <row r="72" ht="13" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901205</t>
+          <t>HASLS22260901333</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>202610121900</t>
+          <t>202610281100</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -6606,17 +6606,17 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>BEER THIP BREWERY (1991) CO., LTD</t>
+          <t>COSMOS BREWERY (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROCK MOUNTAIN SODA </t>
+          <t xml:space="preserve">CHANG SODA WATER </t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -6655,22 +6655,22 @@
     <row r="73" ht="13" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901303</t>
+          <t>HASLS22260901341</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610291300</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -6681,42 +6681,42 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>JPIMI</t>
+          <t>JPKIJ</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>WOODWORKS THAI CO., LTD. (1980)</t>
+          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>FURNITURE (STUDY DESK)</t>
+          <t>FLOURS</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Container Grade A, Underdeck</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P73" s="2" t="n">
         <v>0</v>
@@ -6740,22 +6740,22 @@
     <row r="74" ht="13" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901323</t>
+          <t>HASLS22260901342</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>PCCP</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202611010200</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -6766,36 +6766,36 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPKIJ</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>BEER THIP BREWERY (1991) CO., LTD</t>
+          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHANG SODA WATER </t>
+          <t>FLOURS</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
+          <t>Container Grade A, Underdeck</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N74" s="2" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
     <row r="75" ht="13" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901326</t>
+          <t>HASLS22260901343</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610291300</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPMYJ</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6861,22 +6861,22 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>BEER THIP BREWERY (1991) CO., LTD</t>
+          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHANG SODA WATER </t>
+          <t>FLOURS</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
+          <t>Container Grade A, Underdeck</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
@@ -6910,12 +6910,12 @@
     <row r="76" ht="13" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901328</t>
+          <t>HASLS22260901344</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>PCCP</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>202610201300</t>
+          <t>202611010200</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPMYJ</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6946,22 +6946,22 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>20261017</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>BEER THIP BREWERY (1991) CO., LTD</t>
+          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHANG SODA WATER </t>
+          <t>FLOURS</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
+          <t>Container Grade A, Underdeck</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
@@ -6995,22 +6995,22 @@
     <row r="77" ht="13" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901333</t>
+          <t>HASLS22260901350</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>202610252200</t>
+          <t>202610121900</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -7021,36 +7021,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>COSMOS BREWERY (THAILAND) CO.,LTD.</t>
+          <t>STARPRO STARCH (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHANG SODA WATER </t>
+          <t>STARCH</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N77" s="2" t="n">
         <v>0</v>
@@ -7080,22 +7080,22 @@
     <row r="78" ht="13" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901341</t>
+          <t>HASLS22260901351</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>202610280100</t>
+          <t>202610281100</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -7106,36 +7106,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>JPKIJ</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
+          <t>STARPRO STARCH (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>FLOURS</t>
+          <t>STARCH</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Container Grade A, Underdeck</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N78" s="2" t="n">
         <v>0</v>
@@ -7165,22 +7165,22 @@
     <row r="79" ht="13" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901342</t>
+          <t>HASLS22260901354</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>PCCP</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>202611010200</t>
+          <t>202610110500</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -7191,36 +7191,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>JPKIJ</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
+          <t>ORIENTAL FOODS LIMITED PARTNERSHIP</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>FLOURS</t>
+          <t>RICE STICK</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Container Grade A, Underdeck</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N79" s="2" t="n">
         <v>0</v>
@@ -7250,22 +7250,22 @@
     <row r="80" ht="13" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901343</t>
+          <t>HASLS22260901357</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>202610280100</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -7276,461 +7276,461 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>JPMYJ</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261010</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
+          <t>KORN THAI CO., LTD.</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>FLOURS</t>
+          <t>NON- DAIRY CREAMER</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>Container Grade A, Underdeck</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" ht="13" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901344</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>PCCP</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>202611010200</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>JPMYJ</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>20261022</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>FLOURS</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>Container Grade A, Underdeck</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" ht="13" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901350</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>SWSR</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>202610121900</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x5 </t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>20261006</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>STARPRO STARCH (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>STARCH</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" ht="13" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901351</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>TSXM</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>202610252200</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x4 </t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>STARPRO STARCH (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>STARCH</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="13" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901354</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>DJCF</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>0152N</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>202610110500</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>20261007</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>ORIENTAL FOODS LIMITED PARTNERSHIP</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>RICE STICK</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" ht="13" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901357</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>202610152000</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>20261010</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>KORN THAI CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>NON- DAIRY CREAMER</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>Good, Dry, Clean, No smell, No rust, No dust,
 No bugs/ants, No cracked and good container for
 contain food stuff</t>
         </is>
       </c>
+      <c r="M80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" ht="13" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901358</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>202610121900</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>FRUIT ORGANIC CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>SNACK</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>CLEAN AND GRADE A CTNR</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="13" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901365</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>202610150600</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx6 </t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL ENTECH CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>PARTS OF MACHINERY</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" ht="13" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901389</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SKOR</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>202610202300</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>20261010</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>SUKIJ TANNERY LTD., PART.</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>WET BLUE PIG SKINS</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="13" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901390</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>KMGY</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>202610202130</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>SUKIJ TANNERY LTD., PART.</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>WET BLUE PIG SKINS</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" ht="13" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901392</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>202610281100</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx3 </t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>SUKIJ TANNERY LTD., PART.</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>WET BLUE PIG SKINS</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
       <c r="M85" s="2" t="n">
         <v>0</v>
       </c>
@@ -7738,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="O85" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P85" s="2" t="n">
         <v>0</v>
@@ -7762,7 +7762,7 @@
     <row r="86" ht="13" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901358</t>
+          <t>HASLS22260901393</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>202610121900</t>
+          <t>202611011600</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -7788,42 +7788,42 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>FRUIT ORGANIC CO., LTD.</t>
+          <t>SUKIJ TANNERY LTD., PART.</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>SNACK</t>
+          <t>WET BLUE PIG SKINS</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>CLEAN AND GRADE A CTNR</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P86" s="2" t="n">
         <v>0</v>
@@ -7847,12 +7847,12 @@
     <row r="87" ht="13" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901365</t>
+          <t>HASLS22260901401</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610170100</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -7873,42 +7873,42 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx6 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>EXCEL ENTECH CO.,LTD.</t>
+          <t>GLOBAL FOOD TRADING CO.,LTD.</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>PARTS OF MACHINERY</t>
+          <t>FOOD STUFF</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQUEST CONTAINER FOOD GRADE</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O87" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P87" s="2" t="n">
         <v>0</v>
@@ -7932,22 +7932,22 @@
     <row r="88" ht="13" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901389</t>
+          <t>HASLS22260901419</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SKOR</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>202610200300</t>
+          <t>202610301400</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -7958,42 +7958,42 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261024</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>SUKIJ TANNERY LTD., PART.</t>
+          <t>COSMOS BREWERY (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>WET BLUE PIG SKINS</t>
+          <t xml:space="preserve">CHANG SODA WATER </t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O88" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P88" s="2" t="n">
         <v>0</v>
@@ -8017,22 +8017,22 @@
     <row r="89" ht="13" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901390</t>
+          <t>HASLS22260901437</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>202610201300</t>
+          <t>202610200200</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -8043,42 +8043,42 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>SUKIJ TANNERY LTD., PART.</t>
+          <t>DUNI (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>WET BLUE PIG SKINS</t>
+          <t xml:space="preserve">PAPER NAPKIN </t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQ. GOOD GARDE CONTAINER</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O89" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P89" s="2" t="n">
         <v>0</v>
@@ -8102,22 +8102,22 @@
     <row r="90" ht="13" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901392</t>
+          <t>HASLS22260901443</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>202610281100</t>
+          <t>202610200200</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -8128,27 +8128,27 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>JPTYO</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>SUKIJ TANNERY LTD., PART.</t>
+          <t>TASCO INTERNATIONAL CO., LTD.</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>WET BLUE PIG SKINS</t>
+          <t>FISH MEAL</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8157,13 +8157,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P90" s="2" t="n">
         <v>0</v>
@@ -8187,12 +8187,12 @@
     <row r="91" ht="13" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901393</t>
+          <t>HASLS22260901449</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>202611011600</t>
+          <t>202610241500</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -8213,27 +8213,27 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>JPTYO</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261017</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>SUKIJ TANNERY LTD., PART.</t>
+          <t>TASCO INTERNATIONAL CO., LTD.</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>WET BLUE PIG SKINS</t>
+          <t>FISH MEAL</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P91" s="2" t="n">
         <v>0</v>
@@ -8272,22 +8272,22 @@
     <row r="92" ht="13" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901401</t>
+          <t>HASLS22260901475</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>202610170100</t>
+          <t>202611011600</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -8298,36 +8298,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>GLOBAL FOOD TRADING CO.,LTD.</t>
+          <t>ASIA MODIFIED STARCH CO.,LTD.</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>FOOD STUFF</t>
+          <t xml:space="preserve">MODIFIED STARCH </t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>REQUEST CONTAINER FOOD GRADE</t>
+          <t>Dry &amp; Clean Container (Food Grade) / Container grade A</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N92" s="2" t="n">
         <v>0</v>
@@ -8357,22 +8357,22 @@
     <row r="93" ht="13" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901419</t>
+          <t>HASLS22260901491</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>202610290800</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -8383,32 +8383,32 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>20261024</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>COSMOS BREWERY (THAILAND) CO.,LTD.</t>
+          <t>UCHIYAMA(THAILAND)CO.,LTD.</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHANG SODA WATER </t>
+          <t>SPARE PART</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
+          <t>REQ CLEAN CONTAINER AND GRADE A</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
@@ -8418,7 +8418,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P93" s="2" t="n">
         <v>0</v>
@@ -8442,22 +8442,22 @@
     <row r="94" ht="13" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901437</t>
+          <t>HASLS22260901511</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>202610200200</t>
+          <t>202610191500</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -8468,36 +8468,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>DUNI (THAILAND) CO., LTD.</t>
+          <t>EVERSHINING INGREDIENT CO.,LTD.</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAPER NAPKIN </t>
+          <t>PROTEIN ANIMAL</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>REQ. GOOD GARDE CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N94" s="2" t="n">
         <v>0</v>
@@ -8527,22 +8527,22 @@
     <row r="95" ht="13" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901443</t>
+          <t>HASLS22260901526</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>PCCP</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>202610200200</t>
+          <t>202611010200</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -8553,27 +8553,27 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>JPTYO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261024</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>TASCO INTERNATIONAL CO., LTD.</t>
+          <t>EVERSHINING INGREDIENT CO.,LTD.</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>FISH MEAL</t>
+          <t>PROTEIN ANIMAL FEED</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N95" s="2" t="n">
         <v>0</v>
@@ -8612,12 +8612,12 @@
     <row r="96" ht="13" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901449</t>
+          <t>HASLS22260901547</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>202610241500</t>
+          <t>202610141800</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -8638,42 +8638,42 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>JPTYO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>20261017</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>TASCO INTERNATIONAL CO., LTD.</t>
+          <t>YEARRAKARN CO., LTD.</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>FISH MEAL</t>
+          <t>NON-DAIRY CERAMER</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Food Grade Container Only</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O96" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P96" s="2" t="n">
         <v>0</v>
@@ -8697,22 +8697,22 @@
     <row r="97" ht="13" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901475</t>
+          <t>HASLS22260901595</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>202611011600</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -8733,22 +8733,22 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261010</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>ASIA MODIFIED STARCH CO.,LTD.</t>
+          <t>CHAROEN POKPHAND PRODUCE CO., LTD.</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODIFIED STARCH </t>
+          <t>CORN SEEDS</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Dry &amp; Clean Container (Food Grade) / Container grade A</t>
+          <t>CLEAN AND GOOD CONTAINER GRADE A</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
@@ -8782,12 +8782,12 @@
     <row r="98" ht="13" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901491</t>
+          <t>HASLS22260901886</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610291300</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -8808,42 +8808,42 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx5 </t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20261024</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>UCHIYAMA(THAILAND)CO.,LTD.</t>
+          <t>THAI ASAHI CO., LTD.</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>SPARE PART</t>
+          <t xml:space="preserve">POTATO STARCH </t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>REQ CLEAN CONTAINER AND GRADE A</t>
+          <t>Grade A and food grade container</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P98" s="2" t="n">
         <v>0</v>
@@ -8867,22 +8867,22 @@
     <row r="99" ht="13" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901511</t>
+          <t>HASLS22260901896</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>202610191500</t>
+          <t>202610150600</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -8893,36 +8893,36 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPKIJ</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>EVERSHINING INGREDIENT CO.,LTD.</t>
+          <t>GFM CO., LTD.</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>PROTEIN ANIMAL</t>
+          <t>FLOURS</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Container Grade A</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N99" s="2" t="n">
         <v>0</v>
@@ -8952,22 +8952,22 @@
     <row r="100" ht="13" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901526</t>
+          <t>HASLS22260902001</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>PCCP</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>202611010200</t>
+          <t>202610152100</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -8983,37 +8983,37 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x4 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>20261024</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>EVERSHINING INGREDIENT CO.,LTD.</t>
+          <t>ROYAL CAN INDUSTRIES CO., LTD.</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>PROTEIN ANIMAL FEED</t>
+          <t>EMPTY CANS</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQ FOOD GRADE CONTAINER</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P100" s="2" t="n">
         <v>0</v>
@@ -9037,22 +9037,22 @@
     <row r="101" ht="13" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901547</t>
+          <t>HASLS22260902032</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>202610140800</t>
+          <t>202610291300</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -9063,42 +9063,42 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261024</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>YEARRAKARN CO., LTD.</t>
+          <t>AJINOMOTO CO., (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>NON-DAIRY CERAMER</t>
+          <t>AJITIDE BRAND NUCLEOTIDE I+G</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Food Grade Container Only</t>
+          <t>REQUEST A-GRADE,FOOD GRADE CLEAN AND GOOD CONTAINER</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O101" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P101" s="2" t="n">
         <v>0</v>
@@ -9122,12 +9122,12 @@
     <row r="102" ht="13" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901595</t>
+          <t>HASLS22260902154</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610170100</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
@@ -9148,36 +9148,36 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>CHAROEN POKPHAND PRODUCE CO., LTD.</t>
+          <t>THAI HER CHERN MABLE AND GRANITE CO., LTD.</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>CORN SEEDS</t>
+          <t>MARBLE BLOCK</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>CLEAN AND GOOD CONTAINER GRADE A</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N102" s="2" t="n">
         <v>0</v>
@@ -9207,12 +9207,12 @@
     <row r="103" ht="13" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901886</t>
+          <t>HASLS22260902564</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>202610280100</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -9233,42 +9233,42 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>JPKIJ</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx5 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>20261022</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>THAI ASAHI CO., LTD.</t>
+          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">POTATO STARCH </t>
+          <t>FLOURS</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Grade A and food grade container</t>
+          <t>Container Grade A, Underdeck</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O103" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P103" s="2" t="n">
         <v>0</v>
@@ -9292,12 +9292,12 @@
     <row r="104" ht="13" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901896</t>
+          <t>HASLS22260902752</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>202610152000</t>
+          <t>202610170100</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>JPKIJ</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -9333,17 +9333,17 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>GFM CO., LTD.</t>
+          <t>SAMWON LAMLUKA (THAI LAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>FLOURS</t>
+          <t>MATTRESS, PILLOW</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Container Grade A</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
@@ -9377,7 +9377,7 @@
     <row r="105" ht="13" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902001</t>
+          <t>HASLS22260902811</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>202610151500</t>
+          <t>202610152100</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -9408,31 +9408,31 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>ROYAL CAN INDUSTRIES CO., LTD.</t>
+          <t>KCG CORPORATION PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>EMPTY CANS</t>
+          <t>FOODSTUFF</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>REQ FOOD GRADE CONTAINER</t>
+          <t>CONTAINER FOOD GRADE</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N105" s="2" t="n">
         <v>0</v>
@@ -9462,22 +9462,22 @@
     <row r="106" ht="13" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902032</t>
+          <t>HASLS22260902812</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>202610280100</t>
+          <t>202610152100</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -9493,37 +9493,37 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>AJINOMOTO CO., (THAILAND) LTD.</t>
+          <t>KCG CORPORATION PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>AJITIDE BRAND NUCLEOTIDE I+G</t>
+          <t>FOODSTUFF</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>REQUEST A-GRADE,FOOD GRADE CLEAN AND GOOD CONTAINER</t>
+          <t>CONTAINER FOOD GRADE</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P106" s="2" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
     <row r="107" ht="13" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902154</t>
+          <t>HASLS22261000194</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -9573,42 +9573,42 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx8 </t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>THAI HER CHERN MABLE AND GRANITE CO., LTD.</t>
+          <t>YEARRAKARN CO., LTD.</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>MARBLE BLOCK</t>
+          <t>NON-DAIRY CERAMER</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>RQST CONTAINER 32.5 TONS. // Food Grade Container Only</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O107" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P107" s="2" t="n">
         <v>0</v>
@@ -9632,12 +9632,12 @@
     <row r="108" ht="13" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902564</t>
+          <t>HASLS22261000231</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>202610221330</t>
+          <t>202610291300</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -9658,36 +9658,36 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>JPKIJ</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261024</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
+          <t>AJINOMOTO CO., (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>FLOURS</t>
+          <t>AJITIDE I+G</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Container Grade A, Underdeck</t>
+          <t>PLS ARRANGE GRADE A CONTAINER FOR FOODSTUFF PRODUCT WITH 6 RINGS IN ORDER TO HOOK NET IN THE CONTAINER.</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N108" s="2" t="n">
         <v>0</v>
@@ -9717,22 +9717,22 @@
     <row r="109" ht="13" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902752</t>
+          <t>HASLS22261000246</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>202610170100</t>
+          <t>202610241500</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -9743,42 +9743,42 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>JPKNZ</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>SAMWON LAMLUKA (THAI LAND) CO., LTD.</t>
+          <t>THAI TORAY SYNTHETICS  CO., LTD.</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>MATTRESS, PILLOW</t>
+          <t>YARN</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="N109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P109" s="2" t="n">
         <v>0</v>
@@ -9802,22 +9802,22 @@
     <row r="110" ht="13" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902811</t>
+          <t>HASLS22261000358</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>KUS</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>202610141100</t>
+          <t>202610230100</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -9833,37 +9833,37 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>KCG CORPORATION PUBLIC COMPANY LIMITED</t>
+          <t>THAI TORAY SYNTHETICS  CO., LTD.</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>FOODSTUFF</t>
+          <t>YARN</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>CONTAINER FOOD GRADE</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" s="2" t="n">
         <v>0</v>
@@ -9887,22 +9887,22 @@
     <row r="111" ht="13" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902812</t>
+          <t>HASLS22261000360</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>KUS</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>202610141100</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -9923,22 +9923,22 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>KCG CORPORATION PUBLIC COMPANY LIMITED</t>
+          <t>THAI TORAY SYNTHETICS  CO., LTD.</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>FOODSTUFF</t>
+          <t>YARN</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>CONTAINER FOOD GRADE</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
@@ -9970,189 +9970,104 @@
       </c>
     </row>
     <row r="112" ht="13" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000194</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>202610170100</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr"/>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx8 </t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>20261012</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>YEARRAKARN CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>NON-DAIRY CERAMER</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr">
-        <is>
-          <t>RQST CONTAINER 32.5 TONS. // Food Grade Container Only</t>
-        </is>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" ht="13" customHeight="1">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B113" s="3" t="n"/>
-      <c r="C113" s="3" t="n"/>
-      <c r="D113" s="3" t="n"/>
-      <c r="E113" s="3" t="n"/>
-      <c r="F113" s="3" t="n"/>
-      <c r="G113" s="3" t="n"/>
-      <c r="H113" s="3" t="n"/>
-      <c r="I113" s="3" t="n"/>
-      <c r="J113" s="3" t="n"/>
-      <c r="K113" s="3" t="n"/>
-      <c r="L113" s="3" t="n"/>
-      <c r="M113" s="3">
-        <f>SUM(M2:M112)</f>
+      <c r="B112" s="3" t="n"/>
+      <c r="C112" s="3" t="n"/>
+      <c r="D112" s="3" t="n"/>
+      <c r="E112" s="3" t="n"/>
+      <c r="F112" s="3" t="n"/>
+      <c r="G112" s="3" t="n"/>
+      <c r="H112" s="3" t="n"/>
+      <c r="I112" s="3" t="n"/>
+      <c r="J112" s="3" t="n"/>
+      <c r="K112" s="3" t="n"/>
+      <c r="L112" s="3" t="n"/>
+      <c r="M112" s="3">
+        <f>SUM(M2:M111)</f>
         <v/>
       </c>
-      <c r="N113" s="3">
-        <f>SUM(N2:N112)</f>
+      <c r="N112" s="3">
+        <f>SUM(N2:N111)</f>
         <v/>
       </c>
-      <c r="O113" s="3">
-        <f>SUM(O2:O112)</f>
+      <c r="O112" s="3">
+        <f>SUM(O2:O111)</f>
         <v/>
       </c>
-      <c r="P113" s="3">
-        <f>SUM(P2:P112)</f>
+      <c r="P112" s="3">
+        <f>SUM(P2:P111)</f>
         <v/>
       </c>
-      <c r="Q113" s="3">
-        <f>SUM(Q2:Q112)</f>
+      <c r="Q112" s="3">
+        <f>SUM(Q2:Q111)</f>
         <v/>
       </c>
-      <c r="R113" s="3">
-        <f>SUM(R2:R112)</f>
+      <c r="R112" s="3">
+        <f>SUM(R2:R111)</f>
         <v/>
       </c>
-      <c r="S113" s="3">
-        <f>SUM(S2:S112)</f>
+      <c r="S112" s="3">
+        <f>SUM(S2:S111)</f>
         <v/>
       </c>
-      <c r="T113" s="3">
-        <f>SUM(T2:T112)</f>
+      <c r="T112" s="3">
+        <f>SUM(T2:T111)</f>
         <v/>
       </c>
-      <c r="U113" s="3">
-        <f>SUM(U2:U112)</f>
+      <c r="U112" s="3">
+        <f>SUM(U2:U111)</f>
         <v/>
       </c>
     </row>
+    <row r="115" ht="13" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
+      </c>
+    </row>
     <row r="116" ht="13" customHeight="1">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Smart Logistics Service (Thailand ) Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>247</v>
       </c>
     </row>
     <row r="117" ht="13" customHeight="1">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Smart Logistics Service (Thailand ) Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="118" ht="13" customHeight="1">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B118" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>254</v>
+      <c r="B117" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U112"/>
+  <autoFilter ref="A1:U111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
+++ b/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -607,22 +607,22 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900541</t>
+          <t>HASLS22260900235</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610151200</t>
+          <t>202611020100</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -633,27 +633,27 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>UENO FINE CHEMICALS INDUSTRY (THAILAND) LTD.</t>
+          <t>S. KHONKAEN FOODS PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>MALTITOL SYRUP</t>
+          <t xml:space="preserve">FOODSTUFF </t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -692,22 +692,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900591</t>
+          <t>HASLS22260900867</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610200100</t>
+          <t>202610262300</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -718,42 +718,42 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x25 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20260912</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>DP WORLD LOGISTICS SOLUTIONS (THAILAND) COMPANY LIMITED</t>
+          <t>R.J. LONDON CHEMICAL INDUSTRIES CO., LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>SOYBEAN OIL</t>
+          <t>AUTO ACCESSORIES</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>**APPROVAL BY MR.SANGJUN KIM DD.23/09/2026** *FLEXIBAG* SERVEY 2026-10-12</t>
+          <t>REQUEST GOOD CONTAINER,NO LEAK,NO RUST,NO SCRATCHES,NO OIL,  BECAUSE PRODUCT IN CARTON NO PALLET.</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>0</v>
@@ -777,22 +777,22 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900867</t>
+          <t>HASLS22260901080</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610261800</t>
+          <t>202610210900</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -813,22 +813,22 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>R.J. LONDON CHEMICAL INDUSTRIES CO., LTD.</t>
+          <t>SIAM FUKOKU CO.,LTD.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>AUTO ACCESSORIES</t>
+          <t>BLADE RUBBER</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD CONTAINER,NO LEAK,NO RUST,NO SCRATCHES,NO OIL,  BECAUSE PRODUCT IN CARTON NO PALLET.</t>
+          <t>RQS CLEAN &amp; GOOD CONTAINER CONDITION.</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -860,359 +860,104 @@
       </c>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901138</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>202610141200</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20261007</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>THAI PLASPAC PUBLIC CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>PLATIC CAP</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901401</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>202610181900</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>GLOBAL FOOD TRADING CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>FOOD STUFF</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>REQUEST CONTAINER FOOD GRADE</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902154</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>KJT</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>202610181900</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>THAI HER CHERN MABLE AND GRANITE CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>MARBLE BLOCK</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CTNR</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>0</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3">
+        <f>SUM(M2:M4)</f>
+        <v/>
+      </c>
+      <c r="N5" s="3">
+        <f>SUM(N2:N4)</f>
+        <v/>
+      </c>
+      <c r="O5" s="3">
+        <f>SUM(O2:O4)</f>
+        <v/>
+      </c>
+      <c r="P5" s="3">
+        <f>SUM(P2:P4)</f>
+        <v/>
+      </c>
+      <c r="Q5" s="3">
+        <f>SUM(Q2:Q4)</f>
+        <v/>
+      </c>
+      <c r="R5" s="3">
+        <f>SUM(R2:R4)</f>
+        <v/>
+      </c>
+      <c r="S5" s="3">
+        <f>SUM(S2:S4)</f>
+        <v/>
+      </c>
+      <c r="T5" s="3">
+        <f>SUM(T2:T4)</f>
+        <v/>
+      </c>
+      <c r="U5" s="3">
+        <f>SUM(U2:U4)</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3">
-        <f>SUM(M2:M7)</f>
-        <v/>
-      </c>
-      <c r="N8" s="3">
-        <f>SUM(N2:N7)</f>
-        <v/>
-      </c>
-      <c r="O8" s="3">
-        <f>SUM(O2:O7)</f>
-        <v/>
-      </c>
-      <c r="P8" s="3">
-        <f>SUM(P2:P7)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="3">
-        <f>SUM(Q2:Q7)</f>
-        <v/>
-      </c>
-      <c r="R8" s="3">
-        <f>SUM(R2:R7)</f>
-        <v/>
-      </c>
-      <c r="S8" s="3">
-        <f>SUM(S2:S7)</f>
-        <v/>
-      </c>
-      <c r="T8" s="3">
-        <f>SUM(T2:T7)</f>
-        <v/>
-      </c>
-      <c r="U8" s="3">
-        <f>SUM(U2:U7)</f>
-        <v/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Smart Logistics Service (Thailand ) Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Smart Logistics Service (Thailand ) Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>31</v>
+      <c r="B10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U7"/>
+  <autoFilter ref="A1:U4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
+++ b/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -622,7 +622,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202611020100</t>
+          <t>202611040500</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -692,7 +692,7 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900867</t>
+          <t>HASLS22261001177</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -707,13 +707,13 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610262300</t>
+          <t>202610280700</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -723,37 +723,39 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>R.J. LONDON CHEMICAL INDUSTRIES CO., LTD.</t>
+          <t>GUARDIAN INDUSTRIES CORP LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>AUTO ACCESSORIES</t>
+          <t>CLEAR FLOAT GLASS</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD CONTAINER,NO LEAK,NO RUST,NO SCRATCHES,NO OIL,  BECAUSE PRODUCT IN CARTON NO PALLET.</t>
+          <t>REQUIREMENT1. LOAD UNDER DECK
+2. NEED CONTAINER WITH GOOD CONDITION TO SUPPORT CARGO WEIGHT 24 TONS
+3. NEED WOODEN FLOOR ONLY WITH SMOOTH AND STRE</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>0</v>
@@ -775,189 +777,104 @@
       </c>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901080</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SWAL</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>202610210900</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>SIAM FUKOKU CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>BLADE RUBBER</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>RQS CLEAN &amp; GOOD CONTAINER CONDITION.</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3">
+        <f>SUM(M2:M3)</f>
+        <v/>
+      </c>
+      <c r="N4" s="3">
+        <f>SUM(N2:N3)</f>
+        <v/>
+      </c>
+      <c r="O4" s="3">
+        <f>SUM(O2:O3)</f>
+        <v/>
+      </c>
+      <c r="P4" s="3">
+        <f>SUM(P2:P3)</f>
+        <v/>
+      </c>
+      <c r="Q4" s="3">
+        <f>SUM(Q2:Q3)</f>
+        <v/>
+      </c>
+      <c r="R4" s="3">
+        <f>SUM(R2:R3)</f>
+        <v/>
+      </c>
+      <c r="S4" s="3">
+        <f>SUM(S2:S3)</f>
+        <v/>
+      </c>
+      <c r="T4" s="3">
+        <f>SUM(T2:T3)</f>
+        <v/>
+      </c>
+      <c r="U4" s="3">
+        <f>SUM(U2:U3)</f>
+        <v/>
       </c>
     </row>
-    <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3">
-        <f>SUM(M2:M4)</f>
-        <v/>
-      </c>
-      <c r="N5" s="3">
-        <f>SUM(N2:N4)</f>
-        <v/>
-      </c>
-      <c r="O5" s="3">
-        <f>SUM(O2:O4)</f>
-        <v/>
-      </c>
-      <c r="P5" s="3">
-        <f>SUM(P2:P4)</f>
-        <v/>
-      </c>
-      <c r="Q5" s="3">
-        <f>SUM(Q2:Q4)</f>
-        <v/>
-      </c>
-      <c r="R5" s="3">
-        <f>SUM(R2:R4)</f>
-        <v/>
-      </c>
-      <c r="S5" s="3">
-        <f>SUM(S2:S4)</f>
-        <v/>
-      </c>
-      <c r="T5" s="3">
-        <f>SUM(T2:T4)</f>
-        <v/>
-      </c>
-      <c r="U5" s="3">
-        <f>SUM(U2:U4)</f>
-        <v/>
+    <row r="7" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Smart Logistics Service (Thailand ) Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Smart Logistics Service (Thailand ) Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>3</v>
+      <c r="B9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U4"/>
+  <autoFilter ref="A1:U3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
+++ b/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -622,7 +622,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202611040500</t>
+          <t>202611032300</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -692,7 +692,7 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261001177</t>
+          <t>HASLS22260900561</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -707,45 +707,43 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610280700</t>
+          <t>202610271500</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPKIJ</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>GUARDIAN INDUSTRIES CORP LTD.</t>
+          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>CLEAR FLOAT GLASS</t>
+          <t>FLOURS</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>REQUIREMENT1. LOAD UNDER DECK
-2. NEED CONTAINER WITH GOOD CONDITION TO SUPPORT CARGO WEIGHT 24 TONS
-3. NEED WOODEN FLOOR ONLY WITH SMOOTH AND STRE</t>
+          <t>Container Grade A, Underdeck</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
@@ -755,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>0</v>
@@ -777,104 +775,359 @@
       </c>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3">
-        <f>SUM(M2:M3)</f>
-        <v/>
-      </c>
-      <c r="N4" s="3">
-        <f>SUM(N2:N3)</f>
-        <v/>
-      </c>
-      <c r="O4" s="3">
-        <f>SUM(O2:O3)</f>
-        <v/>
-      </c>
-      <c r="P4" s="3">
-        <f>SUM(P2:P3)</f>
-        <v/>
-      </c>
-      <c r="Q4" s="3">
-        <f>SUM(Q2:Q3)</f>
-        <v/>
-      </c>
-      <c r="R4" s="3">
-        <f>SUM(R2:R3)</f>
-        <v/>
-      </c>
-      <c r="S4" s="3">
-        <f>SUM(S2:S3)</f>
-        <v/>
-      </c>
-      <c r="T4" s="3">
-        <f>SUM(T2:T3)</f>
-        <v/>
-      </c>
-      <c r="U4" s="3">
-        <f>SUM(U2:U3)</f>
-        <v/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000360</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>202610271500</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>THAI TORAY SYNTHETICS  CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>YARN</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="13" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000907</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SWDN</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>202611010800</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>LEE TA RUBBER TREE (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>RECLAIMED RUBBER</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261001043</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>202610271500</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL ENTECH CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>PARTS OF MACHINERY</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3">
+        <f>SUM(M2:M6)</f>
+        <v/>
+      </c>
+      <c r="N7" s="3">
+        <f>SUM(N2:N6)</f>
+        <v/>
+      </c>
+      <c r="O7" s="3">
+        <f>SUM(O2:O6)</f>
+        <v/>
+      </c>
+      <c r="P7" s="3">
+        <f>SUM(P2:P6)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="3">
+        <f>SUM(Q2:Q6)</f>
+        <v/>
+      </c>
+      <c r="R7" s="3">
+        <f>SUM(R2:R6)</f>
+        <v/>
+      </c>
+      <c r="S7" s="3">
+        <f>SUM(S2:S6)</f>
+        <v/>
+      </c>
+      <c r="T7" s="3">
+        <f>SUM(T2:T6)</f>
+        <v/>
+      </c>
+      <c r="U7" s="3">
+        <f>SUM(U2:U6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Pickup Name</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Number of Records</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Total Balance</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Smart Logistics Service (Thailand ) Co.,Ltd.</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>2</v>
+      <c r="B11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>2</v>
+      <c r="B12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U3"/>
+  <autoFilter ref="A1:U6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
+++ b/output/bkg pending - Smart Logistics Service (Thailand ) Co.,Ltd.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -607,22 +607,22 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900235</t>
+          <t>HASLS22260900620</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202611032300</t>
+          <t>202611080400</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -633,7 +633,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -643,22 +643,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>S. KHONKAEN FOODS PUBLIC COMPANY LIMITED</t>
+          <t>VET SUPERIOR CONSULTANT CO., LTD.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOODSTUFF </t>
+          <t>WATER TREATMENT &amp; FEED SUPPLEMENT</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>GOOD CONTAINER</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -690,444 +690,104 @@
       </c>
     </row>
     <row r="3" ht="13" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260900561</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>202610271500</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>JPKIJ</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL FOOD PRODUCTS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>FLOURS</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Container Grade A, Underdeck</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000360</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>202610271500</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>THAI TORAY SYNTHETICS  CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>YARN</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CTNR</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000907</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SWDN</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>202611010800</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>LEE TA RUBBER TREE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>RECLAIMED RUBBER</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3">
+        <f>SUM(M2:M2)</f>
+        <v/>
+      </c>
+      <c r="N3" s="3">
+        <f>SUM(N2:N2)</f>
+        <v/>
+      </c>
+      <c r="O3" s="3">
+        <f>SUM(O2:O2)</f>
+        <v/>
+      </c>
+      <c r="P3" s="3">
+        <f>SUM(P2:P2)</f>
+        <v/>
+      </c>
+      <c r="Q3" s="3">
+        <f>SUM(Q2:Q2)</f>
+        <v/>
+      </c>
+      <c r="R3" s="3">
+        <f>SUM(R2:R2)</f>
+        <v/>
+      </c>
+      <c r="S3" s="3">
+        <f>SUM(S2:S2)</f>
+        <v/>
+      </c>
+      <c r="T3" s="3">
+        <f>SUM(T2:T2)</f>
+        <v/>
+      </c>
+      <c r="U3" s="3">
+        <f>SUM(U2:U2)</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001043</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>202610271500</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>EXCEL ENTECH CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>PARTS OF MACHINERY</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>0</v>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3">
-        <f>SUM(M2:M6)</f>
-        <v/>
-      </c>
-      <c r="N7" s="3">
-        <f>SUM(N2:N6)</f>
-        <v/>
-      </c>
-      <c r="O7" s="3">
-        <f>SUM(O2:O6)</f>
-        <v/>
-      </c>
-      <c r="P7" s="3">
-        <f>SUM(P2:P6)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="3">
-        <f>SUM(Q2:Q6)</f>
-        <v/>
-      </c>
-      <c r="R7" s="3">
-        <f>SUM(R2:R6)</f>
-        <v/>
-      </c>
-      <c r="S7" s="3">
-        <f>SUM(S2:S6)</f>
-        <v/>
-      </c>
-      <c r="T7" s="3">
-        <f>SUM(T2:T6)</f>
-        <v/>
-      </c>
-      <c r="U7" s="3">
-        <f>SUM(U2:U6)</f>
-        <v/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Smart Logistics Service (Thailand ) Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Smart Logistics Service (Thailand ) Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>6</v>
+      <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U6"/>
+  <autoFilter ref="A1:U2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>